--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261023.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261023.xlsx
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.7403092783505154</v>
+        <v>0.7408247422680412</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.09765979381443302</v>
+        <v>0.09817525773195883</v>
       </c>
     </row>
     <row r="8">
@@ -7400,17 +7400,17 @@
     <row r="63">
       <c r="A63" s="19" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P6 骨子案</t>
         </is>
       </c>
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t>見える化 優先度C分野の出力</t>
+          <t>骨子案の作成</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="E63" s="20" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F63" s="20" t="inlineStr">
@@ -7434,16 +7434,16 @@
         </is>
       </c>
       <c r="H63" s="32" t="n">
+        <v>95</v>
+      </c>
+      <c r="I63" s="32" t="n">
         <v>75</v>
       </c>
-      <c r="I63" s="32" t="n">
-        <v>57.8</v>
-      </c>
       <c r="J63" s="32" t="n">
-        <v>17.2</v>
+        <v>20</v>
       </c>
       <c r="K63" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L63" s="33" t="inlineStr">
         <is>
@@ -7452,24 +7452,24 @@
       </c>
       <c r="M63" s="19" t="inlineStr">
         <is>
-          <t>**残るのは医療提供体制・リハビリ提供体制の出力。見える化システムへのアクセスは確保できている（9月28日に推計が通った）**</t>
+          <t>実績データによる数値の確定</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="19" t="inlineStr">
         <is>
-          <t>P6 骨子案</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C64" s="19" t="inlineStr">
         <is>
-          <t>骨子案の作成</t>
+          <t>見える化 優先度C分野の出力</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F64" s="20" t="inlineStr">
@@ -7493,16 +7493,16 @@
         </is>
       </c>
       <c r="H64" s="32" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I64" s="32" t="n">
-        <v>75</v>
+        <v>57.8</v>
       </c>
       <c r="J64" s="32" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="K64" s="20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L64" s="33" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="M64" s="19" t="inlineStr">
         <is>
-          <t>実績データによる数値の確定</t>
+          <t>**残るのは医療提供体制・リハビリ提供体制の出力。見える化システムへのアクセスは確保できている（9月28日に推計が通った）**</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
     <row r="80">
       <c r="A80" s="34" t="inlineStr">
         <is>
-          <t>加重の実績進捗率 74.0％　対　予定進捗率 64.3％　乖離 +9.8ポイント</t>
+          <t>加重の実績進捗率 74.1％　対　予定進捗率 64.3％　乖離 +9.8ポイント</t>
         </is>
       </c>
     </row>
@@ -9948,14 +9948,14 @@
         </is>
       </c>
       <c r="L19" s="22" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M19" s="23" t="n">
         <v>2</v>
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>**10月20日に見える化の出力37ファイルを受領し、素案の第14版に反映。未着はK1-a・K1-b・K2-c・L25、F27は令和3年以降の値。****10月5日に、医療・リハビリ提供体制の出力依頼を作り直した（11_見える化出力依頼）。****8月4日の依頼は在宅医療・介護連携91・医療提供体制62・リハビリ39の計192指標を優先度Cで一括依頼しており、量が多く優先度も低かったため出力されないままだった。****支援Ⅲ（55点・県内39位）の4つの場面ごとの目指すべき姿（決定11）に紐づく46指標へ絞り、1指標ごとに使い道を書いた。依頼する指標が実在することは指標リストと機械照合している。****出力そのものはシステムの操作が要るため、受託者では行えない。****交付金の評価指標は、9月28日に市町村分の集計表を直接受領したため、見える化からの出力は要らなくなった（2-11で整理済み）。****在宅医療・介護連携も、令和8年度交付金の明細により本町の位置（支援Ⅲ 55点・県内39位）が分かっている**</t>
+          <t>**10月23日、見える化からなお要る資料12件（Ａ5・Ｂ4・Ｃ3）を、他団体の案件の依頼項目と突き合わせて整理し、追加の出力依頼を作成した（11_見える化出力依頼）。Ａは事業所分析データ・施設居住系の事業所数・L25・介護保険事業状況報告の設定画面・総括表の再出力（12月の協議会の後）。****10月20日に見える化の出力37ファイルを受領し、素案の第14版に反映。未着はK1-a・K1-b・K2-c・L25、F27は令和3年以降の値。****10月5日に、医療・リハビリ提供体制の出力依頼を作り直した（11_見える化出力依頼）。****8月4日の依頼は在宅医療・介護連携91・医療提供体制62・リハビリ39の計192指標を優先度Cで一括依頼しており、量が多く優先度も低かったため出力されないままだった。****支援Ⅲ（55点・県内39位）の4つの場面ごとの目指すべき姿（決定11）に紐づく46指標へ絞り、1指標ごとに使い道を書いた。依頼する指標が実在することは指標リストと機械照合している。****出力そのものはシステムの操作が要るため、受託者では行えない。****交付金の評価指標は、9月28日に市町村分の集計表を直接受領したため、見える化からの出力は要らなくなった（2-11で整理済み）。****在宅医療・介護連携も、令和8年度交付金の明細により本町の位置（支援Ⅲ 55点・県内39位）が分かっている**</t>
         </is>
       </c>
       <c r="O19" s="19" t="inlineStr">
